--- a/nyc_taxi_analysis/06_evidence/evidence.xlsx
+++ b/nyc_taxi_analysis/06_evidence/evidence.xlsx
@@ -431,12 +431,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -448,8 +448,8 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
     <col width="70" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
@@ -573,45 +573,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ev_e130deeecc58496a</t>
+          <t>ev_2a3db3b226f3412a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>(average_speed_mph / trip_distance)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fare_amount; total_amount</t>
+          <t>average_speed_mph_per_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="F2" t="n">
         <v>3509466</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9656760855932028</v>
+        <v>-0.4255408505515663</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9571350108978417</v>
+        <v>-0.8885380023353529</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4230657610716627</v>
+        <v>0.2505169050856304</v>
       </c>
       <c r="K2" t="n">
-        <v>0.96568</v>
+        <v>0.88854</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,37 +620,37 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9994051036302739</v>
+        <v>0.9968252404271609</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>585c40398a_hexbin.png</t>
+          <t>cdf62daa38_density_trend.png</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive correlation between fare_amount and total_amount with Pearson r = +0.9657 and Spearman rho = +0.9571. The OLS slope is +1.1631 per unit of fare_amount, indicating a strong linear relationship.</t>
+          <t>The relationship between average_speed_mph_per_trip_distance and total_amount is very strong and negative, with a Pearson r of -0.4255 and a Spearman rho of -0.8885. The functional form is inverse, with an R^2 of 0.975, indicating a nonlinear relationship. As average speed increases, the total amount decreases, but the rate of decrease flattens out at higher speeds.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
+          <t>negative; very_strong; pearson_spearman; surprising; stable</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_da530411f5b149ea; ev_d73845be53fe4b4f</t>
+          <t>ev_7c03811495bb4c73; ev_dcfcf8dc308e4a5f; ev_9f6919c622864ac4; ev_2744132d439f4ab1</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,17 +662,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ev_a1f01c44dcee44e1</t>
+          <t>ev_4820137175de4b4b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(trip_distance * trip_duration_minutes)</t>
+          <t>trip_distance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>trip_distance_times_trip_duration_minutes; total_amount</t>
+          <t>trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="F3" t="n">
         <v>3509466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7412647837185244</v>
+        <v>0.867421375892653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.895436231049961</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2878692159217569</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.89544</v>
+        <v>0.86742</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -709,21 +709,21 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.9890844447896711</v>
+        <v>0.9982039731820481</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>f57010fa3f_hexbin.png</t>
+          <t>b74d39221e_density_trend.png</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance_times_trip_duration_minutes and total_amount, with a Pearson correlation of +0.7413 and a Spearman rho of +0.8954 over 3,509,466 rows. The OLS slope is +0.061397 per unit of trip_distance_times_trip_duration_minutes.</t>
+          <t>The statistics show a very strong positive association between trip_distance and total_amount, with a Pearson correlation of +0.8674 and a Spearman rho of +0.8474. The OLS slope is +4.2311 per unit of trip_distance, and the functional form fitted to the conditional mean is linear with an R^2 of 0.993. The mean total_amount increases from 17.15 to 90.55 as trip_distance increases.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ev_da530411f5b149ea; ev_15790f95b6ee4821; ev_a033bea8a3224f1d; ev_6be90678e0a84126; ev_b9e490560198409e; ev_9002df4acd8f4f05</t>
+          <t>ev_6ce484a36f734ab8; ev_e25407702c0447e0; ev_5ee0cbe57c4b4c4a; ev_1c4b7fde6719462b</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -747,17 +747,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ev_01da41bb6c804816</t>
+          <t>ev_b79d45d26895414e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>log(trip_distance)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>trip_duration_minutes; total_amount</t>
+          <t>log_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F4" t="n">
         <v>3509466</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6988447428794324</v>
+        <v>0.7001671976609333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8885383452608312</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2504791798501583</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88854</v>
+        <v>0.84738</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -794,21 +794,21 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.9976225394976196</v>
+        <v>0.9982482859237006</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>8ff62c05a9_hexbin.png</t>
+          <t>6de2708a55_density_trend.png</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_duration_minutes and total_amount, with a Pearson correlation of +0.6988 and a Spearman rho of +0.8885. The OLS slope is +1.0388 per unit of trip_duration_minutes. The hexbin plot illustrates this relationship with a dense clustering along the line of best fit.</t>
+          <t>The statistics show a very strong positive association between log_trip_distance and total_amount, with a Pearson correlation of +0.7002 and a Spearman rho of +0.8474. The relationship is materially nonlinear, with a quadratic fit achieving R^2 = 0.977 on the conditional mean, indicating a strong fit. The OLS slope is +14.071 per unit of log_trip_distance.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -818,13 +818,13 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ev_b9e490560198409e; ev_40f4924458d243d1; ev_8a3e989e8157441a; ev_5abcbb73a1e0468e</t>
+          <t>ev_ff55bcf22cd84394; ev_6ce484a36f734ab8; ev_2a782f5da7c54eb2; ev_1c4b7fde6719462b</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>2 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -836,38 +836,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ev_22740fa3572c4e6e</t>
+          <t>ev_d50daed6805b4473</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>(trip_distance / passenger_count)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>trip_distance; total_amount</t>
+          <t>trip_distance_per_passenger_count; total_amount</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="F5" t="n">
-        <v>3509466</v>
+        <v>2501017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.867421375892653</v>
+        <v>0.8452322269398832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8473806505494269</v>
+        <v>0.8337291006756795</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2182241498046474</v>
       </c>
       <c r="K5" t="n">
-        <v>0.86742</v>
+        <v>0.84523</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -879,33 +882,40 @@
           <t>very strong</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>0.9986338932760329</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>b74d39221e_hexbin.png</t>
+          <t>5d42bca8aa_density_trend.png</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance and total_amount, with a Pearson correlation of +0.8674 and a Spearman rho of +0.8474. The OLS slope is +4.2311 per unit of trip_distance.</t>
+          <t>The statistics show a very strong positive association between trip_distance_per_passenger_count and total_amount, with a Pearson correlation of +0.8452 and Spearman rho of +0.8337. The fitted linear model suggests that for each unit increase in trip_distance_per_passenger_count, the total_amount increases by approximately 4.571 USD. The conditional mean of total_amount rises from 14.73 to 88.56 USD as trip_distance_per_passenger_count increases.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; mechanical</t>
+          <t>positive; very_strong; pearson_spearman; stable</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ev_ff55bcf22cd84394; ev_6ce484a36f734ab8; ev_e23b8715764f4a00; ev_da530411f5b149ea</t>
+          <t>ev_71c8edf73e9340da; ev_5ee0cbe57c4b4c4a; ev_ac82c22c807845b4; ev_e23b8715764f4a00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>'due to' asserts causation, but the evidence is an observational association with no identification strategy</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -915,17 +925,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ev_5547f96e7fa744bf</t>
+          <t>ev_428ee888e36c4b9f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(fare_amount / trip_distance)</t>
+          <t>(passenger_count * trip_distance)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fare_amount / trip_distance; total_amount</t>
+          <t>passenger_count_times_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -934,22 +944,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04054402311080481</v>
+        <v>0.7806523699016266</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4522641312943602</v>
+        <v>0.8348451180254627</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0677329656948885</v>
+        <v>0.2175543936821757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.45226</v>
+        <v>0.83485</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -958,40 +968,39 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
+          <t>very strong</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9974243750597225</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2fc81ea1a5_hexbin.png</t>
+          <t>f16adabba4_density_trend.png</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>The relationship between fare_amount/trip_distance and total_amount shows a weak positive linear association (Pearson r = +0.0405) and a moderate negative monotonic association (Spearman rho = -0.4523). The normalized mutual information is 0.0677, indicating a weak association.</t>
+          <t>The relationship between passenger_count_times_trip_distance and total_amount shows a very strong positive association, with a Pearson correlation of +0.7807 and a Spearman rho of +0.8348. The OLS slope is +2.3402, indicating that for each unit increase in passenger_count_times_trip_distance, the total_amount increases by approximately $2.34. The functional form is linear with an R^2 of 0.977 on the conditional mean.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>positive; moderate; pearson_spearman; mechanical</t>
+          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_ff55bcf22cd84394; ev_da530411f5b149ea</t>
+          <t>ev_4d5e655d4d3d4d74; ev_3406ff235c84430d; ev_311acd0158b0454a; ev_d2789b8b222443aa</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact; total_amount is defined as the sum of fare_amount, extra, mta_tax, tip_amount, tolls_amount, improvement_surcharge, congestion_surcharge, airport_fee, cbd_congestion_fee; its relationship with fare_amount is mechanical, not an empirical finding</t>
-        </is>
-      </c>
+      <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1001,38 +1010,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ev_18f103a535b642e1</t>
+          <t>ev_0cf3a8a7ef4d4dde</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>log(trip_distance)</t>
+          <t>(average_speed_mph * trip_distance)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>log_trip_distance; total_amount</t>
+          <t>average_speed_mph_times_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F7" t="n">
         <v>3509466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7001671976609333</v>
+        <v>0.7788165655343621</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8473806505494269</v>
+        <v>0.726311957694207</v>
       </c>
       <c r="K7" t="n">
-        <v>0.84738</v>
+        <v>0.77882</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1041,40 +1050,36 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6de2708a55_hexbin.png</t>
+          <t>4371399e65_density_trend.png</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log_trip_distance and total_amount, with a Pearson correlation of +0.7002 and a Spearman rho of +0.8474. The OLS slope is +14.071 per unit of log_trip_distance.</t>
+          <t>The relationship between total_amount and average_speed_mph_times_trip_distance is strong and positive, with a Pearson correlation of +0.7788 and a Spearman rho of +0.7263. The quadratic fit shows an R^2 of 0.988, indicating a strong nonlinear relationship. The total_amount increases with average_speed_mph_times_trip_distance, with the mean of total_amount rising from 19.63 to 86.12 USD as average_speed_mph_times_trip_distance increases.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; mechanical</t>
+          <t>positive; strong; pearson_spearman</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>ev_ff55bcf22cd84394; ev_6ce484a36f734ab8; ev_1c4b7fde6719462b; ev_e25407702c0447e0</t>
+          <t>ev_de68a10b4a7e4455; ev_4635f45571544179; ev_6ce484a36f734ab8; ev_15790f95b6ee4821</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
-        </is>
-      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1084,17 +1089,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ev_3b75c4dc9d0f4b7a</t>
+          <t>ev_11e5c44dd4774171</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(trip_distance / trip_duration_minutes)</t>
+          <t>(fare_per_mile * trip_distance)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trip_distance_per_trip_duration_minutes; total_amount</t>
+          <t>fare_per_mile_times_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1103,19 +1108,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>3509466</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5473835801360865</v>
+        <v>0.9656760855932028</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3531235693623642</v>
+        <v>0.957081097824685</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4216936873096108</v>
       </c>
       <c r="K8" t="n">
-        <v>0.54738</v>
+        <v>0.96568</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1124,32 +1132,35 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
+          <t>very strong</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9994051036302739</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>880f84238d_hexbin.png</t>
+          <t>f1c1efba63_density_trend.png</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a positive association between trip_distance_per_trip_duration_minutes and total_amount with a Pearson correlation of +0.5474 and a Spearman rho of +0.3531. The OLS slope is +104.1 per unit of trip_distance_per_trip_duration_minutes.</t>
+          <t>The total amount charged to passengers is very strongly associated with fare_per_mile_times_trip_distance, with a Pearson correlation of +0.9657 and Spearman rho of +0.9571 over 3,509,466 rows. The relationship is positive and linear, with the conditional mean of total_amount increasing from 11.86 to 96.17 as fare_per_mile_times_trip_distance increases.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>positive; strong; pearson_spearman; mechanical</t>
+          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>ev_da530411f5b149ea; ev_b9e490560198409e; ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a</t>
+          <t>ev_f0e8684d508548d6; ev_026780a90ef04463; ev_ed418bb4e7384b93; ev_2abb782d7ab5479a</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1163,41 +1174,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ev_03280601ea95405c</t>
+          <t>ev_946845877d1c47b9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(trip_duration_minutes / trip_distance)</t>
+          <t>log1p(trip_distance)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>trip_duration_minutes_per_trip_distance; total_amount</t>
+          <t>log1p_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>3509466</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02612619849158769</v>
+        <v>0.8041207183735763</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3531239375169539</v>
+        <v>0.8473806505494269</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04916244729839663</v>
+        <v>0.2292361220782569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.35312</v>
+        <v>0.84738</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1206,40 +1217,39 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
+          <t>very strong</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9989294984333846</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>68230704e6_hexbin.png</t>
+          <t>f141556f75_density_trend.png</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>The relationship between trip_duration_minutes_per_trip_distance and total_amount shows a weak positive linear association (Pearson r = +0.0261) and a moderate negative monotonic association (Spearman rho = -0.3531). The normalized mutual information is 0.0492, indicating low shared information. The OLS slope is +0.003692, suggesting a slight increase in total_amount with trip_duration_minutes_per_trip_distance.</t>
+          <t>The statistics show a very strong positive association between log1p_trip_distance and total_amount, with a Pearson correlation of +0.8041 and a Spearman rho of +0.8474. The OLS slope is +24.895 per unit of log1p_trip_distance. The quadratic fit has an R^2 of 0.988, indicating a materially nonlinear relationship. The mean total_amount increases from 17.15 to 90.55 as log1p_trip_distance increases.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>positive; moderate; pearson_spearman</t>
+          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>ev_b9e490560198409e; ev_da530411f5b149ea; ev_40f4924458d243d1; ev_e23b8715764f4a00</t>
+          <t>ev_70499596ba254788; ev_d6b08c4209a94902; ev_2e7ebdd04ce24085; ev_6ce484a36f734ab8</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
-        </is>
-      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1249,17 +1259,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ev_8dd1e8fe121a4599</t>
+          <t>ev_8f3f87e007964eba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_type groups</t>
+          <t>(fare_per_mile / trip_distance)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>payment_type; fare_amount</t>
+          <t>fare_per_mile_per_trip_distance; total_amount</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1268,56 +1278,65 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F10" t="n">
         <v>3509466</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.1521138756208264</v>
+      <c r="G10" t="n">
+        <v>0.04057522932726527</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.7371659713029562</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1590559465344401</v>
       </c>
       <c r="K10" t="n">
-        <v>0.15211</v>
+        <v>0.73717</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>weak</t>
-        </is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9694052765740944</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>grp:paymen_box.png</t>
+          <t>f3e14fa57f_density_trend.png</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>The mean fare amounts for different payment types are: Flex Fare trip ($25.17), Credit card ($19.32), Cash ($19.43), No charge ($19.41), and Dispute ($23.49). The eta squared value of 0.1521 indicates a weak association between payment type and fare amount.</t>
+          <t>The relationship between fare_per_mile_per_trip_distance and total_amount shows a strong inverse association with a Spearman rho of -0.7372. The functional form is inverse, with a fitted curve of y = 19.43 + 15.04/x, achieving an R^2 of 0.983. The Pearson correlation is weakly positive at +0.0406, indicating a negligible linear relationship.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>undetermined; weak; grouped_eta_squared; mechanical</t>
+          <t>positive; strong; pearson_spearman; mechanical; stable</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ev_f47e17fcd87f474c; ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_da530411f5b149ea</t>
+          <t>ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_1c4b7fde6719462b; ev_da530411f5b149ea</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>payment_type is categorical; compared as group means, not as a correlation</t>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact; total_amount is defined as the sum of fare_amount, extra, mta_tax, tip_amount, tolls_amount, improvement_surcharge, congestion_surcharge, airport_fee, cbd_congestion_fee; its relationship with fare_amount is mechanical, not an empirical finding</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1329,17 +1348,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ev_030121cde85e4d91</t>
+          <t>ev_f69fdc515b1d4f7a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>log1p(trip_distance)</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>log1p_trip_distance; total_amount</t>
+          <t>fare_per_mile; total_amount</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1348,22 +1367,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
         <v>3509466</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8041207183735763</v>
+        <v>0.04054402311080481</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8473806505494269</v>
+        <v>-0.4522641312943602</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2292361220782569</v>
+        <v>0.0677329656948885</v>
       </c>
       <c r="K11" t="n">
-        <v>0.84738</v>
+        <v>0.45226</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1372,39 +1391,40 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>very strong</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0.9989294984333846</v>
+          <t>moderate</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>f141556f75_hexbin.png</t>
+          <t>118c265b17_density_trend.png</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log1p_trip_distance and total_amount, with a Pearson correlation of +0.8041 and a Spearman rho of +0.8474. The OLS slope is +24.895 per unit of log1p_trip_distance. The hexbin plot indicates a dense concentration of data points along the line of best fit, suggesting a strong linear relationship.</t>
+          <t>The relationship between fare_per_mile and total_amount shows a weak positive linear correlation (Pearson r = +0.0405) and a moderate negative monotonic correlation (Spearman rho = -0.4523). The functional form fitted to the conditional mean is inverse, with R^2 = 0.695, indicating a nonlinear relationship. The mean total_amount decreases from 54.58 to 30.81 as fare_per_mile increases.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
+          <t>positive; moderate; pearson_spearman; mechanical</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>ev_d6b08c4209a94902; ev_ff55bcf22cd84394; ev_15790f95b6ee4821; ev_a033bea8a3224f1d</t>
+          <t>ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_4269147516914790; ev_1c4b7fde6719462b</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; 3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form; most subgroups show the opposite sign to the pooled correlation; the pooled value is an aggregation artifact</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1414,17 +1434,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ev_73df613937424df8</t>
+          <t>ev_b1c7a87c598f49d7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(trip_distance / passenger_count)</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>trip_distance_per_passenger_count; total_amount</t>
+          <t>trip_duration_minutes; total_amount</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1436,19 +1456,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2501017</v>
+        <v>3509466</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8452322269398832</v>
+        <v>0.6988447428794324</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8337291006756795</v>
+        <v>0.8885383452608312</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2182241498046474</v>
+        <v>0.2504791798501583</v>
       </c>
       <c r="K12" t="n">
-        <v>0.84523</v>
+        <v>0.88854</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1461,21 +1481,21 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.9986338932760329</v>
+        <v>0.9976225394976196</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>5d42bca8aa_hexbin.png</t>
+          <t>8ff62c05a9_density_trend.png</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance_per_passenger_count and total_amount, with a Pearson correlation of +0.8452 and a Spearman rho of +0.8337. The OLS slope is +4.4983, indicating that for each unit increase in trip_distance_per_passenger_count, the total_amount increases by approximately $4.50.</t>
+          <t>The statistics show a very strong positive association between trip_duration_minutes and total_amount, with a Pearson correlation of +0.6988 and a Spearman rho of +0.8885. The OLS slope is +1.0388 per unit of trip_duration_minutes. The functional form is linear, with the conditional mean of total_amount increasing from 12.93 to 73.64 as trip_duration_minutes increases.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1485,11 +1505,15 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ev_e23b8715764f4a00; ev_1c4b7fde6719462b; ev_5fe78b09f4cd401a; ev_5ee0cbe57c4b4c4a</t>
+          <t>ev_b9e490560198409e; ev_80d34605b6b045cc; ev_991c30c994024b1d; ev_8b8777bd1f714e10</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>3 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1499,41 +1523,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ev_4d5e655d4d3d4d74</t>
+          <t>ev_a0e6bb1d2bd94e2c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(passenger_count * trip_distance)</t>
+          <t>(trip_duration_minutes / tip_fraction_of_fare)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>passenger_count_times_trip_distance; total_amount</t>
+          <t>trip_duration_minutes_per_tip_fraction_of_fare; total_amount</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>explained</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="F13" t="n">
-        <v>2515206</v>
+        <v>2065405</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7806523699016266</v>
+        <v>0.04690825126404342</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8348451180254627</v>
+        <v>0.8097285115033341</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2175543936821757</v>
+        <v>0.1957703996238391</v>
       </c>
       <c r="K13" t="n">
-        <v>0.83485</v>
+        <v>0.8097299999999999</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1546,35 +1570,39 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.9974243750597225</v>
+        <v>0.8707572031218791</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>f16adabba4_hexbin.png</t>
+          <t>edbd559ad6_density_trend.png</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>The relationship between passenger_count_times_trip_distance and total_amount shows a very strong positive association, with a Pearson correlation of +0.7807 and a Spearman rho of +0.8348. The OLS slope is +2.3402, indicating that for each unit increase in passenger_count_times_trip_distance, the total_amount increases by approximately 2.34 USD. The cross-fold stability is 0.997, indicating consistent results across different data subsets.</t>
+          <t>The relationship between trip_duration_minutes_per_tip_fraction_of_fare and total_amount is positive and very strong, with a Spearman rho of +0.8097. The relationship is nonlinear, best described by a quadratic function with an R^2 of 0.990. The total_amount increases with trip_duration_minutes_per_tip_fraction_of_fare, but the rate of increase slows down as the value of x increases, saturating near a turning point of x = 320.7.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; stable</t>
+          <t>positive; very_strong; pearson_spearman; mechanical; stable</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ev_311acd0158b0454a; ev_8a3e989e8157441a; ev_5abcbb73a1e0468e; ev_5ee0cbe57c4b4c4a</t>
+          <t>ev_b9e490560198409e; ev_40f4924458d243d1; ev_da530411f5b149ea; ev_8a3e989e8157441a</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear; total_amount is defined as the sum of fare_amount, extra, mta_tax, tip_amount, tolls_amount, improvement_surcharge, congestion_surcharge, airport_fee, cbd_congestion_fee; its relationship with fare_amount, tip_amount is mechanical, not an empirical finding</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
@@ -1584,84 +1612,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ev_24a0da8d14304bf0</t>
+          <t>ev_b1355be178d74319</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(passenger_count / trip_distance)</t>
+          <t>is_airport_pickup groups</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>passenger_count_per_trip_distance; total_amount</t>
+          <t>is_airport_pickup; total_amount</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F14" t="n">
         <v>2515206</v>
       </c>
-      <c r="G14" t="n">
-        <v>-0.1591283294608796</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.8212728592035911</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.2139136151440717</v>
+      <c r="I14" t="n">
+        <v>0.6426310816003343</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8212699999999999</v>
+        <v>0.64263</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>very strong</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>0.9391456907199275</v>
+          <t>strong</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>db5734034b_hexbin.png</t>
+          <t>grp_is_air_box.png</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>The relationship between passenger_count_per_trip_distance and total_amount shows a very strong negative monotonic association (Spearman rho = -0.8213) and a weaker negative linear association (Pearson r = -0.1591). The OLS slope is -1.2715 per unit of passenger_count_per_trip_distance.</t>
+          <t>The mean total amount for non-airport pickups (is_airport_pickup=0.0) is $24.36, while for airport pickups (is_airport_pickup=1.0) it is $75.37. The eta squared value is 0.6426, indicating a strong variance explained by the group.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>negative; very_strong; pearson_spearman; surprising; stable</t>
+          <t>undetermined; strong; grouped_eta_squared; mechanical</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>ev_e23b8715764f4a00; ev_5ee0cbe57c4b4c4a; ev_1c4b7fde6719462b; ev_ff55bcf22cd84394</t>
+          <t>ev_e609254137a0495e; ev_f1023570905442b7; ev_ddd668636e8c4624; ev_94e07d8c01394c58</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>monotonic association is much stronger than the linear one; the relationship is probably nonlinear</t>
+          <t>is_airport_pickup is categorical; compared as group means, not as a correlation</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1673,17 +1692,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ev_5f943dfd00eb4476</t>
+          <t>ev_7732a65757b5434f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>log(trip_duration_minutes)</t>
+          <t>RatecodeID groups</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>log_trip_duration_minutes; total_amount</t>
+          <t>RatecodeID; total_amount</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1692,153 +1711,59 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.849</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="n">
-        <v>3509466</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.6849326881994786</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.8885383452608312</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.2504791798501583</v>
+        <v>2515206</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6788292533749694</v>
       </c>
       <c r="K15" t="n">
-        <v>0.88854</v>
+        <v>0.67883</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>very strong</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>0.9992393614921484</v>
+          <t>strong</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ef027e69ae_hexbin.png</t>
+          <t>grp_Rateco_box.png</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log_trip_duration_minutes and total_amount, with a Pearson correlation of +0.6849 and a Spearman rho of +0.8885. The OLS slope is +19.826 per unit of log_trip_duration_minutes.</t>
+          <t>The RatecodeID is strongly associated with the total_amount passengers pay for NYC yellow taxi trips, with an eta squared of 0.6788. The group means show that trips with RatecodeID 4 (Nassau or Westchester) have the highest mean total amount ($135.6), while RatecodeID 6 (Group ride) has the lowest ($4.5).</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>positive; very_strong; pearson_spearman; stable</t>
+          <t>undetermined; strong; grouped_eta_squared</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>ev_b9e490560198409e; ev_40f4924458d243d1; ev_da530411f5b149ea; ev_8a3e989e8157441a</t>
+          <t>ev_f3a4251a84624d99; ev_5ee0cbe57c4b4c4a; ev_e23b8715764f4a00; ev_5fe78b09f4cd401a</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>1 equivalent transformation(s) of the same columns gave the same effect within 0.01; reporting the simplest form; 'due to' asserts causation, but the evidence is an observational association with no identification strategy</t>
+          <t>RatecodeID is categorical; compared as group means, not as a correlation</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
-        <is>
-          <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ev_991c30c994024b1d</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>(passenger_count * trip_duration_minutes)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>passenger_count_times_trip_duration_minutes; total_amount</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>explained</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2515206</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.6343146751956786</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.8389135286620988</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.2180679896208855</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.83891</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>very strong</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>0.9964803378062043</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>hexbin</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>160a090832_hexbin.png</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>The data shows a very strong positive association between passenger_count_times_trip_duration_minutes and total_amount, with a Pearson correlation of +0.6343 and a Spearman rho of +0.8389. The OLS slope is +0.61356 per unit of passenger_count_times_trip_duration_minutes.</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>positive; very_strong; pearson_spearman; stable</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ev_40f4924458d243d1; ev_8a3e989e8157441a; ev_5abcbb73a1e0468e; ev_da530411f5b149ea</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
         <is>
           <t>positive_distance; plausible_distance; non_negative_fare; non_negative_total; plausible_duration; bounded_duration; plausible_speed</t>
         </is>
